--- a/exports/PNB_full_report.xlsx
+++ b/exports/PNB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.22</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>36.78</v>
+        <v>35.79</v>
       </c>
       <c r="I2" t="n">
         <v>36.3070024963788</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.42</v>
+        <v>-4.07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.68</v>
+        <v>4.45</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="O2" t="n">
         <v>3.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>7.54</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44586.55208333334</v>
+        <v>44588.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>37.26</v>
+        <v>38.2</v>
       </c>
       <c r="I3" t="n">
         <v>37.94247324111051</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.11</v>
+        <v>-6.73</v>
       </c>
       <c r="L3" t="n">
-        <v>4.36</v>
+        <v>6.87</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.11</v>
+        <v>4.43</v>
       </c>
       <c r="O3" t="n">
         <v>-2.69</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.66</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>37.54</v>
+        <v>36.07</v>
       </c>
       <c r="I4" t="n">
         <v>37.43123361871106</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.73</v>
+        <v>-5.58</v>
       </c>
       <c r="L4" t="n">
-        <v>3.72</v>
+        <v>6.54</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>4.16</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>6.55</v>
       </c>
       <c r="O4" t="n">
         <v>4.43</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.84</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44634.38541666666</v>
+        <v>44634.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>33.9</v>
+        <v>34.71</v>
       </c>
       <c r="I5" t="n">
         <v>34.41687640612537</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>6.02</v>
+        <v>3.77</v>
       </c>
       <c r="L5" t="n">
         <v>2.38</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>34.66</v>
+        <v>33.81</v>
       </c>
       <c r="I6" t="n">
         <v>33.99159453490415</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.14</v>
+        <v>-2.59</v>
       </c>
       <c r="L6" t="n">
         <v>5.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="N6" t="n">
         <v>2.33</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.14</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>28.67</v>
+        <v>29.99</v>
       </c>
       <c r="I7" t="n">
         <v>29.53952855482641</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="L7" t="n">
         <v>2.22</v>
@@ -840,7 +923,7 @@
         <v>1.87</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>4.08</v>
       </c>
       <c r="O7" t="n">
         <v>-1.36</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>29.13</v>
+        <v>28.42</v>
       </c>
       <c r="I8" t="n">
         <v>28.60650454651926</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.87</v>
+        <v>-5.24</v>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>5.84</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.92</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>2.27</v>
       </c>
       <c r="O8" t="n">
         <v>4.08</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.43</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44746.55208333334</v>
+        <v>44747.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>28.34</v>
+        <v>28.37</v>
       </c>
       <c r="I9" t="n">
         <v>28.35260620551092</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="L9" t="n">
         <v>1.51</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.44</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>31.45</v>
+        <v>30.74</v>
       </c>
       <c r="I10" t="n">
         <v>30.89191424683202</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K10" t="n">
-        <v>10.86</v>
+        <v>8.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.62</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.31</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44797.55208333334</v>
+        <v>44798.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>31.64</v>
+        <v>33.29</v>
       </c>
       <c r="I11" t="n">
         <v>32.26220315638816</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.93</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>3.22</v>
+        <v>8.91</v>
       </c>
       <c r="M11" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="N11" t="n">
-        <v>1.99</v>
+        <v>5.21</v>
       </c>
       <c r="O11" t="n">
         <v>-2.54</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.91</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44827.38541666666</v>
+        <v>44827.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>36.31</v>
+        <v>35.98</v>
       </c>
       <c r="I12" t="n">
         <v>36.16400171155348</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>9.07</v>
+        <v>8.08</v>
       </c>
       <c r="L12" t="n">
         <v>4.69</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>8.85</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44851.55208333334</v>
+        <v>44852.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>34.99</v>
+        <v>36.64</v>
       </c>
       <c r="I13" t="n">
         <v>36.04551843521461</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>2.75</v>
+        <v>-1.83</v>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="M13" t="n">
         <v>2.22</v>
       </c>
       <c r="N13" t="n">
-        <v>3.49</v>
+        <v>4.97</v>
       </c>
       <c r="O13" t="n">
         <v>-6.06</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.32</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>40.08</v>
+        <v>37.77</v>
       </c>
       <c r="I14" t="n">
         <v>38.00717618570739</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>9.390000000000001</v>
+        <v>3.08</v>
       </c>
       <c r="L14" t="n">
         <v>4.5</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>13.47</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44872.55208333334</v>
+        <v>44874.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>39.67</v>
+        <v>42.54</v>
       </c>
       <c r="I15" t="n">
         <v>40.63649830112234</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.03</v>
+        <v>-12.63</v>
       </c>
       <c r="L15" t="n">
-        <v>8.869999999999999</v>
+        <v>15.01</v>
       </c>
       <c r="M15" t="n">
         <v>2.38</v>
       </c>
       <c r="N15" t="n">
-        <v>6.13</v>
+        <v>6.65</v>
       </c>
       <c r="O15" t="n">
         <v>-6.88</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>11.68</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44914.55208333334</v>
+        <v>44915.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>52.93</v>
+        <v>51.66</v>
       </c>
       <c r="I16" t="n">
         <v>52.45769805039154</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>24.42</v>
+        <v>21.44</v>
       </c>
       <c r="L16" t="n">
         <v>6.56</v>
       </c>
       <c r="M16" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="N16" t="n">
         <v>3.95</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>10.23</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>52.7</v>
+        <v>53.36</v>
       </c>
       <c r="I17" t="n">
         <v>53.32655288973108</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.01</v>
+        <v>-3.29</v>
       </c>
       <c r="L17" t="n">
-        <v>4.37</v>
+        <v>4.76</v>
       </c>
       <c r="M17" t="n">
         <v>1.5</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>52.27</v>
+        <v>51.09</v>
       </c>
       <c r="I18" t="n">
         <v>51.98948412845773</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.04</v>
+        <v>-4.25</v>
       </c>
       <c r="L18" t="n">
-        <v>3.37</v>
+        <v>5.94</v>
       </c>
       <c r="M18" t="n">
         <v>0.28</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.35</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>46.89</v>
+        <v>48.78</v>
       </c>
       <c r="I19" t="n">
         <v>47.83174982491826</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K19" t="n">
-        <v>8.220000000000001</v>
+        <v>4.52</v>
       </c>
       <c r="L19" t="n">
         <v>2.6</v>
@@ -1524,7 +1751,7 @@
         <v>6.37</v>
       </c>
       <c r="N19" t="n">
-        <v>3.73</v>
+        <v>4.33</v>
       </c>
       <c r="O19" t="n">
         <v>-2.72</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>7.25</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>47.22</v>
+        <v>46.37</v>
       </c>
       <c r="I20" t="n">
         <v>46.37705669922208</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.2</v>
+        <v>-4.94</v>
       </c>
       <c r="L20" t="n">
-        <v>4.47</v>
+        <v>5.33</v>
       </c>
       <c r="M20" t="n">
         <v>0.79</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>4.33</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.43</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45029.38541666666</v>
+        <v>45029.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>44.53</v>
+        <v>45.05</v>
       </c>
       <c r="I21" t="n">
         <v>44.79466408853784</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>3.97</v>
+        <v>2.85</v>
       </c>
       <c r="L21" t="n">
         <v>2.33</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.87</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45054.55208333334</v>
+        <v>45055.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>49.2</v>
+        <v>47.97</v>
       </c>
       <c r="I22" t="n">
         <v>48.18728034832107</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>9.210000000000001</v>
+        <v>6.48</v>
       </c>
       <c r="L22" t="n">
         <v>1.47</v>
@@ -1695,7 +1958,7 @@
         <v>1.62</v>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>3.56</v>
       </c>
       <c r="O22" t="n">
         <v>1.28</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.98</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45076.38541666666</v>
+        <v>45076.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>48.26</v>
+        <v>48.64</v>
       </c>
       <c r="I23" t="n">
         <v>48.47781961138724</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="L23" t="n">
         <v>3.46</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45092.38541666666</v>
+        <v>45092.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>48.59</v>
+        <v>47.55</v>
       </c>
       <c r="I24" t="n">
         <v>47.78043999847351</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1</v>
+        <v>-2.24</v>
       </c>
       <c r="L24" t="n">
-        <v>1.07</v>
+        <v>2.53</v>
       </c>
       <c r="M24" t="n">
         <v>0.21</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.6</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45097.55208333334</v>
+        <v>45098.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>49.11</v>
+        <v>50.05</v>
       </c>
       <c r="I25" t="n">
         <v>49.73663730883371</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.28</v>
+        <v>-5.26</v>
       </c>
       <c r="L25" t="n">
-        <v>4.27</v>
+        <v>5.36</v>
       </c>
       <c r="M25" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
         <v>-2.52</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.62</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>47.88</v>
+        <v>47.6</v>
       </c>
       <c r="I26" t="n">
         <v>47.63605787818445</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.34</v>
+        <v>-4.9</v>
       </c>
       <c r="L26" t="n">
         <v>5.37</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.64</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45107.55208333334</v>
+        <v>45110.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>48.78</v>
+        <v>49.96</v>
       </c>
       <c r="I27" t="n">
         <v>49.75811383163633</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.48</v>
+        <v>-4.96</v>
       </c>
       <c r="L27" t="n">
-        <v>2.67</v>
+        <v>5.06</v>
       </c>
       <c r="M27" t="n">
-        <v>0.29</v>
+        <v>0.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.07</v>
+        <v>4.24</v>
       </c>
       <c r="O27" t="n">
         <v>-1.47</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.35</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>57.94</v>
+        <v>56.1</v>
       </c>
       <c r="I28" t="n">
         <v>56.90900628227397</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K28" t="n">
-        <v>15.97</v>
+        <v>12.29</v>
       </c>
       <c r="L28" t="n">
         <v>1.7</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.9</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45155.38541666666</v>
+        <v>45155.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>59.12</v>
+        <v>59.78</v>
       </c>
       <c r="I29" t="n">
         <v>59.25501811266164</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.38</v>
+        <v>-6.56</v>
       </c>
       <c r="L29" t="n">
         <v>7.58</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.9</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45203.55208333334</v>
+        <v>45204.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>75.22</v>
+        <v>72.39</v>
       </c>
       <c r="I30" t="n">
         <v>72.724121789481</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>25.83</v>
+        <v>21.09</v>
       </c>
       <c r="L30" t="n">
         <v>3.4</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.3</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45231.55208333334</v>
+        <v>45232.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>68.94</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>69.57369252923262</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>4.77</v>
+        <v>3.2</v>
       </c>
       <c r="L31" t="n">
         <v>5.73</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>73.47</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I32" t="n">
         <v>72.15668931281471</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>4.85</v>
+        <v>2.9</v>
       </c>
       <c r="L32" t="n">
         <v>0.9399999999999999</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>6.56</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45260.55208333334</v>
+        <v>45261.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>73.56999999999999</v>
+        <v>75.55</v>
       </c>
       <c r="I33" t="n">
         <v>74.83465979271519</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.04</v>
+        <v>-4.79</v>
       </c>
       <c r="L33" t="n">
-        <v>4.59</v>
+        <v>6.74</v>
       </c>
       <c r="M33" t="n">
         <v>0.51</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.93</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>85.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="I34" t="n">
         <v>82.29566094448616</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>12.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>2.44</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>8.02</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>87.02</v>
+        <v>90.95</v>
       </c>
       <c r="I35" t="n">
         <v>87.87412317146959</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.28</v>
+        <v>-11.08</v>
       </c>
       <c r="L35" t="n">
-        <v>6.28</v>
+        <v>11.19</v>
       </c>
       <c r="M35" t="n">
         <v>0.9</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.6</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>116.58</v>
+        <v>113.61</v>
       </c>
       <c r="I36" t="n">
         <v>114.2580687284488</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K36" t="n">
-        <v>28.18</v>
+        <v>24.91</v>
       </c>
       <c r="L36" t="n">
         <v>3.64</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.65</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45356.38541666666</v>
+        <v>45356.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>121.4</v>
+        <v>122.54</v>
       </c>
       <c r="I37" t="n">
         <v>122.3473454426441</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.86</v>
+        <v>-7.86</v>
       </c>
       <c r="L37" t="n">
-        <v>7.06</v>
+        <v>8.06</v>
       </c>
       <c r="M37" t="n">
         <v>2.89</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>7.39</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>118.99</v>
+        <v>113.7</v>
       </c>
       <c r="I38" t="n">
         <v>115.7519586610237</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.9</v>
+        <v>-7.21</v>
       </c>
       <c r="L38" t="n">
-        <v>3.79</v>
+        <v>8.52</v>
       </c>
       <c r="M38" t="n">
         <v>0.12</v>
       </c>
       <c r="N38" t="n">
-        <v>1.9</v>
+        <v>5.95</v>
       </c>
       <c r="O38" t="n">
         <v>2.98</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.35</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>118.47</v>
+        <v>119.7</v>
       </c>
       <c r="I39" t="n">
         <v>119.0323204204235</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.2</v>
+        <v>-5.28</v>
       </c>
       <c r="L39" t="n">
-        <v>5.36</v>
+        <v>5.44</v>
       </c>
       <c r="M39" t="n">
         <v>1.36</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>122.91</v>
+        <v>121.45</v>
       </c>
       <c r="I40" t="n">
         <v>121.4821756674474</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>2.68</v>
+        <v>1.46</v>
       </c>
       <c r="L40" t="n">
         <v>1.42</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.24</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45408.38541666666</v>
+        <v>45408.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>129</v>
+        <v>129.14</v>
       </c>
       <c r="I41" t="n">
         <v>129.025424772454</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.22</v>
+        <v>-6.33</v>
       </c>
       <c r="L41" t="n">
         <v>7.39</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>5.14</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>128.34</v>
+        <v>120.51</v>
       </c>
       <c r="I42" t="n">
         <v>125.1444183146029</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.62</v>
+        <v>-6.68</v>
       </c>
       <c r="L42" t="n">
-        <v>1.83</v>
+        <v>6.88</v>
       </c>
       <c r="M42" t="n">
         <v>0.04</v>
       </c>
       <c r="N42" t="n">
-        <v>1.7</v>
+        <v>6.47</v>
       </c>
       <c r="O42" t="n">
         <v>0.77</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>11.64</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>122.11</v>
+        <v>130.04</v>
       </c>
       <c r="I43" t="n">
         <v>124.8272117520205</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.33</v>
+        <v>-7.91</v>
       </c>
       <c r="L43" t="n">
-        <v>7.28</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>1.85</v>
+        <v>4.41</v>
       </c>
       <c r="N43" t="n">
-        <v>3.13</v>
+        <v>5.95</v>
       </c>
       <c r="O43" t="n">
         <v>-6.47</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>129.38</v>
+        <v>109.64</v>
       </c>
       <c r="I44" t="n">
         <v>121.3512317747827</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.51</v>
+        <v>-15.69</v>
       </c>
       <c r="L44" t="n">
-        <v>3.67</v>
+        <v>24.32</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>15.22</v>
       </c>
       <c r="O44" t="n">
         <v>5.95</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>19.13</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>113.09</v>
+        <v>120.81</v>
       </c>
       <c r="I45" t="n">
         <v>115.626818305806</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.15</v>
+        <v>-10.19</v>
       </c>
       <c r="L45" t="n">
         <v>17.48</v>
       </c>
       <c r="M45" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="N45" t="n">
-        <v>4.18</v>
+        <v>5.99</v>
       </c>
       <c r="O45" t="n">
         <v>-15.22</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>113.7</v>
+        <v>108.01</v>
       </c>
       <c r="I46" t="n">
         <v>112.5421252241598</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.89</v>
+        <v>-10.6</v>
       </c>
       <c r="L46" t="n">
-        <v>6.54</v>
+        <v>11.51</v>
       </c>
       <c r="M46" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.96</v>
+        <v>5.48</v>
       </c>
       <c r="O46" t="n">
         <v>5.99</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.65</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45600.38541666666</v>
+        <v>45600.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>95.89</v>
+        <v>97.92</v>
       </c>
       <c r="I47" t="n">
         <v>96.35706283581762</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>91</v>
+        <v>91.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>11.22</v>
+        <v>9.34</v>
       </c>
       <c r="L47" t="n">
         <v>3.16</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>9.19</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45610.38541666666</v>
+        <v>45610.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>95.45999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I48" t="n">
         <v>94.57617787283417</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.51</v>
+        <v>-3.9</v>
       </c>
       <c r="L48" t="n">
-        <v>3.56</v>
+        <v>4.24</v>
       </c>
       <c r="M48" t="n">
         <v>0.8100000000000001</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.18</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>98.42</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>98.79405144046697</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.59</v>
+        <v>-5.28</v>
       </c>
       <c r="L49" t="n">
         <v>5.86</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>7.36</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>99.91</v>
+        <v>97.81</v>
       </c>
       <c r="I50" t="n">
         <v>98.80670959176184</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K50" t="n">
-        <v>0.85</v>
+        <v>-1.27</v>
       </c>
       <c r="L50" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="M50" t="n">
         <v>0.74</v>
       </c>
       <c r="N50" t="n">
-        <v>2.19</v>
+        <v>2.56</v>
       </c>
       <c r="O50" t="n">
         <v>0.84</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.98</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45660.38541666666</v>
+        <v>45660.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>100.22</v>
+        <v>100.6</v>
       </c>
       <c r="I51" t="n">
         <v>100.5604055378292</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.46</v>
+        <v>-2.85</v>
       </c>
       <c r="L51" t="n">
         <v>3.55</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5.05</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>96.33</v>
+        <v>94.47</v>
       </c>
       <c r="I52" t="n">
         <v>95.51694766930629</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.24</v>
+        <v>-6.09</v>
       </c>
       <c r="L52" t="n">
-        <v>5.43</v>
+        <v>7.25</v>
       </c>
       <c r="M52" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="N52" t="n">
         <v>4.39</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.06</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>94.73</v>
+        <v>96.84</v>
       </c>
       <c r="I53" t="n">
         <v>96.25473970519768</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.28</v>
+        <v>-2.51</v>
       </c>
       <c r="L53" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="M53" t="n">
         <v>1.14</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.38</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>91.70999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="I54" t="n">
         <v>90.37046574114014</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.3</v>
+        <v>-6.72</v>
       </c>
       <c r="L54" t="n">
         <v>7.69</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.4</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>86.31999999999999</v>
+        <v>87.37</v>
       </c>
       <c r="I55" t="n">
         <v>86.7482258510655</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>52</v>
+        <v>52.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>4.44</v>
+        <v>3.28</v>
       </c>
       <c r="L55" t="n">
         <v>6.63</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.37</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>93.95999999999999</v>
+        <v>91.31</v>
       </c>
       <c r="I56" t="n">
         <v>93.26017152782511</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K56" t="n">
-        <v>7.54</v>
+        <v>4.51</v>
       </c>
       <c r="L56" t="n">
         <v>2.63</v>
@@ -3633,7 +4304,7 @@
         <v>5.95</v>
       </c>
       <c r="N56" t="n">
-        <v>3.51</v>
+        <v>5.12</v>
       </c>
       <c r="O56" t="n">
         <v>2.12</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.53</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>92.43000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I57" t="n">
         <v>92.4966618951953</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.23</v>
+        <v>-1.41</v>
       </c>
       <c r="L57" t="n">
         <v>3.66</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>5.38</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>101.89</v>
+        <v>100.58</v>
       </c>
       <c r="I58" t="n">
         <v>101.505045353398</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>10.03</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L58" t="n">
         <v>0.3</v>
       </c>
       <c r="M58" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.49</v>
       </c>
       <c r="N58" t="n">
         <v>2.17</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>4.43</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>100.77</v>
+        <v>102.85</v>
       </c>
       <c r="I59" t="n">
         <v>101.8311766543409</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.19</v>
+        <v>-2.26</v>
       </c>
       <c r="L59" t="n">
-        <v>1.8</v>
+        <v>3.01</v>
       </c>
       <c r="M59" t="n">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
       <c r="N59" t="n">
         <v>3.12</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.85</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>109.52</v>
+        <v>107.04</v>
       </c>
       <c r="I60" t="n">
         <v>107.3608427462334</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K60" t="n">
-        <v>6.49</v>
+        <v>4.07</v>
       </c>
       <c r="L60" t="n">
         <v>0.88</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.76</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>101.38</v>
+        <v>103.23</v>
       </c>
       <c r="I61" t="n">
         <v>101.903157717859</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>5.29</v>
+        <v>3.56</v>
       </c>
       <c r="L61" t="n">
         <v>2.67</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>108.02</v>
+        <v>105.2</v>
       </c>
       <c r="I62" t="n">
         <v>106.8333134956668</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K62" t="n">
-        <v>4.64</v>
+        <v>1.91</v>
       </c>
       <c r="L62" t="n">
         <v>1.54</v>
@@ -3975,7 +4718,7 @@
         <v>0.08</v>
       </c>
       <c r="N62" t="n">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="O62" t="n">
         <v>1.93</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.02</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45929.55208333334</v>
+        <v>45930.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>106.72</v>
+        <v>109.59</v>
       </c>
       <c r="I63" t="n">
         <v>109.3798194415885</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.44</v>
+        <v>-4.17</v>
       </c>
       <c r="L63" t="n">
-        <v>2.84</v>
+        <v>5.03</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N63" t="n">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="O63" t="n">
         <v>-2.93</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.67</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>121.47</v>
+        <v>116.8</v>
       </c>
       <c r="I64" t="n">
         <v>118.2146910067399</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K64" t="n">
-        <v>10.84</v>
+        <v>6.58</v>
       </c>
       <c r="L64" t="n">
         <v>2.59</v>
@@ -4089,7 +4856,7 @@
         <v>0.42</v>
       </c>
       <c r="N64" t="n">
-        <v>1.96</v>
+        <v>4.04</v>
       </c>
       <c r="O64" t="n">
         <v>2.9</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.37</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46021.38541666666</v>
+        <v>46021.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>118.26</v>
+        <v>118.8</v>
       </c>
       <c r="I65" t="n">
         <v>118.4779364267532</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.25</v>
+        <v>-1.71</v>
       </c>
       <c r="L65" t="n">
         <v>4.62</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>3.92</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>124.71</v>
+        <v>121.91</v>
       </c>
       <c r="I66" t="n">
         <v>123.4397166432007</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>4.97</v>
+        <v>2.62</v>
       </c>
       <c r="L66" t="n">
         <v>0.93</v>
       </c>
       <c r="M66" t="n">
-        <v>0.04</v>
+        <v>0.34</v>
       </c>
       <c r="N66" t="n">
         <v>2.93</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46069.55208333334</v>
+        <v>46070.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>117.44</v>
+        <v>121.54</v>
       </c>
       <c r="I67" t="n">
         <v>120.607104571149</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>3.67</v>
+        <v>0.3</v>
       </c>
       <c r="L67" t="n">
         <v>3.9</v>
@@ -4260,7 +5063,7 @@
         <v>3.91</v>
       </c>
       <c r="N67" t="n">
-        <v>2.71</v>
+        <v>3.35</v>
       </c>
       <c r="O67" t="n">
         <v>-2.31</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.26</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>122.69</v>
+        <v>118.18</v>
       </c>
       <c r="I68" t="n">
         <v>121.3044497769543</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K68" t="n">
-        <v>0.95</v>
+        <v>-2.76</v>
       </c>
       <c r="L68" t="n">
         <v>4.21</v>
@@ -4317,7 +5132,7 @@
         <v>3.06</v>
       </c>
       <c r="N68" t="n">
-        <v>2.12</v>
+        <v>3.86</v>
       </c>
       <c r="O68" t="n">
         <v>3.35</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.21</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>101.6</v>
+        <v>107.13</v>
       </c>
       <c r="I69" t="n">
         <v>105.9106703735938</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>14.03</v>
+        <v>9.35</v>
       </c>
       <c r="L69" t="n">
         <v>2.7</v>
       </c>
       <c r="M69" t="n">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="N69" t="n">
-        <v>3.68</v>
+        <v>6.5</v>
       </c>
       <c r="O69" t="n">
         <v>-3.86</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.94</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>108.14</v>
+        <v>106.1</v>
       </c>
       <c r="I70" t="n">
         <v>106.6252283410345</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.96</v>
       </c>
       <c r="L70" t="n">
         <v>2.2</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.07</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>99.97</v>
+        <v>102.56</v>
       </c>
       <c r="I71" t="n">
         <v>102.0589299751885</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K71" t="n">
-        <v>5.78</v>
+        <v>3.34</v>
       </c>
       <c r="L71" t="n">
         <v>2.34</v>
@@ -4488,7 +5339,7 @@
         <v>2.23</v>
       </c>
       <c r="N71" t="n">
-        <v>2.15</v>
+        <v>3.48</v>
       </c>
       <c r="O71" t="n">
         <v>-1.53</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>5.7</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>106.86</v>
+        <v>104.93</v>
       </c>
       <c r="I72" t="n">
         <v>105.4053125152536</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K72" t="n">
-        <v>4.19</v>
+        <v>2.31</v>
       </c>
       <c r="L72" t="n">
         <v>2.72</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>4.86</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46212.55208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>103.7</v>
+        <v>106.45</v>
       </c>
       <c r="I73" t="n">
         <v>106.1473641014313</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K73" t="n">
-        <v>1.17</v>
+        <v>-1.45</v>
       </c>
       <c r="L73" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="M73" t="n">
         <v>0.5</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>5.73</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>116.25</v>
+        <v>113.59</v>
       </c>
       <c r="I74" t="n">
         <v>114.566943961294</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>77.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K74" t="n">
-        <v>9.210000000000001</v>
+        <v>6.71</v>
       </c>
       <c r="L74" t="n">
         <v>2.57</v>
@@ -4659,7 +5546,7 @@
         <v>1.07</v>
       </c>
       <c r="N74" t="n">
-        <v>1.95</v>
+        <v>3.23</v>
       </c>
       <c r="O74" t="n">
         <v>1.81</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>5.05</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>114.5</v>
+        <v>116.33</v>
       </c>
       <c r="I75" t="n">
         <v>115.6979448446873</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.8</v>
+        <v>-2.41</v>
       </c>
       <c r="L75" t="n">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
       <c r="M75" t="n">
         <v>0.5600000000000001</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4776,6 +5687,12 @@
       <c r="Q76" t="n">
         <v>26</v>
       </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6878,7 +7795,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="6">
@@ -6888,7 +7805,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="7">
@@ -6898,7 +7815,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="8">
@@ -6908,7 +7825,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6918,7 +7835,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="10">
@@ -6928,7 +7845,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47.2</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="11">
@@ -6938,7 +7855,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -6948,7 +7865,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -6958,7 +7875,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78.40000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -6968,7 +7885,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.63</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="15">
@@ -6978,7 +7895,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.75</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="16">
@@ -6988,7 +7905,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="17">
@@ -6998,7 +7915,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.18</v>
+        <v>24.91</v>
       </c>
     </row>
     <row r="18">
@@ -7008,7 +7925,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.6</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="19">
@@ -7018,7 +7935,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.77</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="20">
@@ -7028,7 +7945,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.38</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="21">
@@ -7038,7 +7955,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.48</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="22">
@@ -7048,7 +7965,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -7058,7 +7975,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -7068,7 +7985,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="25">
@@ -7088,7 +8005,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="27">
@@ -7098,7 +8015,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.880000000000001</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="28">
@@ -7108,7 +8025,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
